--- a/MBP_Cold_Email_Follow_Up_Report.xlsx
+++ b/MBP_Cold_Email_Follow_Up_Report.xlsx
@@ -54,11 +54,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="003F3F3F"/>
+      <color rgb="009C6500"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C6500"/>
+      <color rgb="003F3F3F"/>
     </font>
     <font>
       <b val="1"/>
@@ -125,12 +125,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -202,8 +202,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,13 +223,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr"/>
@@ -2767,12 +2767,12 @@
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr"/>
@@ -2812,12 +2812,12 @@
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
@@ -2857,12 +2857,12 @@
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr"/>
@@ -2906,12 +2906,12 @@
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr"/>
@@ -2955,12 +2955,12 @@
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr"/>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr"/>
@@ -3049,12 +3049,12 @@
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr"/>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr"/>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr"/>
@@ -3188,12 +3188,12 @@
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr"/>
@@ -3286,12 +3286,12 @@
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr"/>
@@ -3335,12 +3335,12 @@
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr"/>
@@ -3380,12 +3380,12 @@
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr"/>
@@ -3425,12 +3425,12 @@
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr"/>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr"/>
@@ -3519,12 +3519,12 @@
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr"/>
@@ -3564,12 +3564,12 @@
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr"/>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="I59" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr"/>
@@ -3658,12 +3658,12 @@
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr"/>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="I61" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr"/>
@@ -3756,12 +3756,12 @@
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr"/>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr"/>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr"/>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr"/>
@@ -3936,12 +3936,12 @@
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr"/>
@@ -3981,12 +3981,12 @@
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr"/>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr"/>
@@ -4079,12 +4079,12 @@
       </c>
       <c r="I69" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr"/>
@@ -4124,12 +4124,12 @@
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr"/>
@@ -4173,12 +4173,12 @@
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr"/>
@@ -4222,12 +4222,12 @@
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr"/>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr"/>
@@ -4316,12 +4316,12 @@
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr"/>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr"/>
@@ -4406,12 +4406,12 @@
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J76" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K76" s="7" t="inlineStr"/>
@@ -4455,12 +4455,12 @@
       </c>
       <c r="I77" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr"/>
@@ -4504,12 +4504,12 @@
       </c>
       <c r="I78" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K78" s="7" t="inlineStr"/>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J80" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K80" s="7" t="inlineStr"/>
@@ -4647,12 +4647,12 @@
       </c>
       <c r="I81" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr"/>
@@ -4692,12 +4692,12 @@
       </c>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J82" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K82" s="7" t="inlineStr"/>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr"/>
@@ -4786,12 +4786,12 @@
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K84" s="7" t="inlineStr"/>
@@ -4831,12 +4831,12 @@
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr"/>
@@ -4876,12 +4876,12 @@
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J86" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K86" s="7" t="inlineStr"/>
@@ -4921,12 +4921,12 @@
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr"/>
@@ -4966,12 +4966,12 @@
       </c>
       <c r="I88" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K88" s="7" t="inlineStr"/>
@@ -5015,12 +5015,12 @@
       </c>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr"/>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="I90" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K90" s="7" t="inlineStr"/>
@@ -5109,12 +5109,12 @@
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr"/>
@@ -5154,12 +5154,12 @@
       </c>
       <c r="I92" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr"/>
@@ -5199,12 +5199,12 @@
       </c>
       <c r="I93" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr"/>
@@ -5248,12 +5248,12 @@
       </c>
       <c r="I94" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr"/>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="I95" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr"/>
@@ -5342,12 +5342,12 @@
       </c>
       <c r="I96" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K96" s="7" t="inlineStr"/>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="I97" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr"/>
@@ -5436,12 +5436,12 @@
       </c>
       <c r="I98" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J98" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K98" s="7" t="inlineStr"/>
@@ -5481,12 +5481,12 @@
       </c>
       <c r="I99" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr"/>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="I100" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K100" s="7" t="inlineStr"/>
@@ -5575,12 +5575,12 @@
       </c>
       <c r="I101" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr"/>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="I103" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr"/>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="I104" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K104" s="7" t="inlineStr"/>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="I105" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr"/>
@@ -5816,12 +5816,12 @@
       </c>
       <c r="I106" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K106" s="7" t="inlineStr"/>
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I107" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr"/>
@@ -5906,12 +5906,12 @@
       </c>
       <c r="I108" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K108" s="7" t="inlineStr"/>
@@ -5949,7 +5949,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I109" s="10" t="inlineStr">
+      <c r="I109" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -6000,12 +6000,12 @@
       </c>
       <c r="I110" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K110" s="7" t="inlineStr"/>
@@ -6045,12 +6045,12 @@
       </c>
       <c r="I111" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr"/>
@@ -6094,12 +6094,12 @@
       </c>
       <c r="I112" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K112" s="7" t="inlineStr"/>
@@ -6137,7 +6137,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I113" s="10" t="inlineStr">
+      <c r="I113" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -6184,12 +6184,12 @@
       </c>
       <c r="I114" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K114" s="7" t="inlineStr"/>
@@ -6229,12 +6229,12 @@
       </c>
       <c r="I115" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr"/>
@@ -6274,12 +6274,12 @@
       </c>
       <c r="I116" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K116" s="7" t="inlineStr"/>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="I117" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr"/>
@@ -6368,12 +6368,12 @@
       </c>
       <c r="I118" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K118" s="7" t="inlineStr"/>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="I119" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr"/>
@@ -6462,12 +6462,12 @@
       </c>
       <c r="I120" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K120" s="7" t="inlineStr"/>
@@ -6507,12 +6507,12 @@
       </c>
       <c r="I121" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr"/>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="I122" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K122" s="7" t="inlineStr"/>
@@ -6597,12 +6597,12 @@
       </c>
       <c r="I123" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr"/>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="I124" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K124" s="7" t="inlineStr"/>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="I125" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr"/>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="I127" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="I129" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr"/>
@@ -6932,12 +6932,12 @@
       </c>
       <c r="I130" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K130" s="7" t="inlineStr"/>
@@ -6977,12 +6977,12 @@
       </c>
       <c r="I131" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr"/>
@@ -7026,12 +7026,12 @@
       </c>
       <c r="I132" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K132" s="7" t="inlineStr"/>
@@ -7071,12 +7071,12 @@
       </c>
       <c r="I133" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr"/>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="I134" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K134" s="7" t="inlineStr"/>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="I136" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J136" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K136" s="7" t="inlineStr"/>
@@ -7263,12 +7263,12 @@
       </c>
       <c r="I137" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr"/>
@@ -7312,12 +7312,12 @@
       </c>
       <c r="I138" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J138" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K138" s="7" t="inlineStr"/>
@@ -7357,12 +7357,12 @@
       </c>
       <c r="I139" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr"/>
@@ -7406,12 +7406,12 @@
       </c>
       <c r="I140" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J140" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K140" s="7" t="inlineStr"/>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="I141" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr"/>
@@ -7549,12 +7549,12 @@
       </c>
       <c r="I143" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J143" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr"/>
@@ -7592,7 +7592,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I144" s="10" t="inlineStr">
+      <c r="I144" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -7643,12 +7643,12 @@
       </c>
       <c r="I145" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J145" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr"/>
@@ -7692,12 +7692,12 @@
       </c>
       <c r="I146" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J146" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K146" s="7" t="inlineStr"/>
@@ -7737,12 +7737,12 @@
       </c>
       <c r="I147" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J147" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr"/>
@@ -7782,12 +7782,12 @@
       </c>
       <c r="I148" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K148" s="7" t="inlineStr"/>
@@ -7827,12 +7827,12 @@
       </c>
       <c r="I149" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J149" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr"/>
@@ -7876,12 +7876,12 @@
       </c>
       <c r="I150" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K150" s="7" t="inlineStr"/>
@@ -7925,12 +7925,12 @@
       </c>
       <c r="I151" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J151" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr"/>
@@ -7974,12 +7974,12 @@
       </c>
       <c r="I152" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J152" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K152" s="7" t="inlineStr"/>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="I155" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J155" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr"/>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="I157" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J157" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr"/>
@@ -8268,12 +8268,12 @@
       </c>
       <c r="I158" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J158" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K158" s="7" t="inlineStr"/>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="I159" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J159" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr"/>
@@ -8366,12 +8366,12 @@
       </c>
       <c r="I160" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J160" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K160" s="7" t="inlineStr"/>
@@ -8411,12 +8411,12 @@
       </c>
       <c r="I161" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J161" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr"/>
@@ -8456,12 +8456,12 @@
       </c>
       <c r="I162" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J162" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K162" s="7" t="inlineStr"/>
@@ -8501,12 +8501,12 @@
       </c>
       <c r="I163" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J163" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr"/>
@@ -8546,12 +8546,12 @@
       </c>
       <c r="I164" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J164" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K164" s="7" t="inlineStr"/>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="I165" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J165" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr"/>
@@ -8636,12 +8636,12 @@
       </c>
       <c r="I166" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J166" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K166" s="7" t="inlineStr"/>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="I167" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J167" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr"/>
@@ -8734,12 +8734,12 @@
       </c>
       <c r="I168" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J168" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K168" s="7" t="inlineStr"/>
@@ -8779,12 +8779,12 @@
       </c>
       <c r="I169" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J169" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I170" s="10" t="inlineStr">
+      <c r="I170" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -8918,12 +8918,12 @@
       </c>
       <c r="I172" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J172" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K172" s="7" t="inlineStr"/>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="I173" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J173" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr"/>
@@ -9098,12 +9098,12 @@
       </c>
       <c r="I176" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K176" s="7" t="inlineStr"/>
@@ -9192,12 +9192,12 @@
       </c>
       <c r="I178" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J178" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K178" s="7" t="inlineStr"/>
@@ -9290,12 +9290,12 @@
       </c>
       <c r="I180" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J180" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding. Note: Check in Q2 2026</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play. Note: Check in Q2 2026</t>
         </is>
       </c>
       <c r="K180" s="7" t="inlineStr"/>
@@ -9335,12 +9335,12 @@
       </c>
       <c r="I181" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J181" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr"/>
@@ -9384,12 +9384,12 @@
       </c>
       <c r="I182" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding. Note: Check in Q2 2026</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play. Note: Check in Q2 2026</t>
         </is>
       </c>
       <c r="K182" s="7" t="inlineStr"/>
@@ -9482,12 +9482,12 @@
       </c>
       <c r="I184" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K184" s="7" t="inlineStr"/>
@@ -9576,12 +9576,12 @@
       </c>
       <c r="I186" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J186" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K186" s="7" t="inlineStr"/>
@@ -9619,7 +9619,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I187" s="10" t="inlineStr">
+      <c r="I187" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="I188" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K188" s="7" t="inlineStr"/>
@@ -9713,7 +9713,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I189" s="10" t="inlineStr">
+      <c r="I189" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -9760,12 +9760,12 @@
       </c>
       <c r="I190" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J190" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K190" s="7" t="inlineStr"/>
@@ -9809,12 +9809,12 @@
       </c>
       <c r="I191" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J191" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K191" s="4" t="inlineStr"/>
@@ -9907,12 +9907,12 @@
       </c>
       <c r="I193" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J193" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K193" s="4" t="inlineStr"/>
@@ -9999,7 +9999,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I195" s="10" t="inlineStr">
+      <c r="I195" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -10101,7 +10101,7 @@
           <t>Meeting Scheduled</t>
         </is>
       </c>
-      <c r="I197" s="11" t="inlineStr">
+      <c r="I197" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -10146,7 +10146,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I198" s="10" t="inlineStr">
+      <c r="I198" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -10193,12 +10193,12 @@
       </c>
       <c r="I199" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J199" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K199" s="4" t="inlineStr"/>
@@ -10242,12 +10242,12 @@
       </c>
       <c r="I200" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J200" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K200" s="7" t="inlineStr"/>
@@ -10287,12 +10287,12 @@
       </c>
       <c r="I201" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J201" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K201" s="4" t="inlineStr"/>
@@ -10330,7 +10330,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I202" s="10" t="inlineStr">
+      <c r="I202" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -10377,12 +10377,12 @@
       </c>
       <c r="I203" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J203" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K203" s="4" t="inlineStr"/>
@@ -10477,7 +10477,7 @@
           <t>Meeting Scheduled</t>
         </is>
       </c>
-      <c r="I205" s="11" t="inlineStr">
+      <c r="I205" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -10528,12 +10528,12 @@
       </c>
       <c r="I206" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J206" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K206" s="7" t="inlineStr"/>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="I207" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J207" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K207" s="4" t="inlineStr"/>
@@ -10618,12 +10618,12 @@
       </c>
       <c r="I208" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J208" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K208" s="7" t="inlineStr"/>
@@ -10661,7 +10661,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I209" s="10" t="inlineStr">
+      <c r="I209" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -10757,12 +10757,12 @@
       </c>
       <c r="I211" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J211" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K211" s="4" t="inlineStr"/>
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I212" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J212" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K212" s="7" t="inlineStr"/>
@@ -10841,7 +10841,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I213" s="10" t="inlineStr">
+      <c r="I213" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -10949,12 +10949,12 @@
       </c>
       <c r="I215" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J215" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K215" s="4" t="inlineStr"/>
@@ -10994,12 +10994,12 @@
       </c>
       <c r="I216" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J216" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K216" s="7" t="inlineStr"/>
@@ -11039,12 +11039,12 @@
       </c>
       <c r="I217" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J217" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K217" s="4" t="inlineStr"/>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="I218" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J218" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K218" s="7" t="inlineStr"/>
@@ -11133,12 +11133,12 @@
       </c>
       <c r="I219" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J219" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K219" s="4" t="inlineStr"/>
@@ -11176,7 +11176,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I220" s="10" t="inlineStr">
+      <c r="I220" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -11270,7 +11270,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I222" s="10" t="inlineStr">
+      <c r="I222" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -11321,12 +11321,12 @@
       </c>
       <c r="I223" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J223" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K223" s="4" t="inlineStr"/>
@@ -11364,7 +11364,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I224" s="10" t="inlineStr">
+      <c r="I224" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -11415,12 +11415,12 @@
       </c>
       <c r="I225" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J225" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K225" s="4" t="inlineStr"/>
@@ -11566,12 +11566,12 @@
       </c>
       <c r="I228" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J228" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K228" s="7" t="inlineStr"/>
@@ -11664,12 +11664,12 @@
       </c>
       <c r="I230" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J230" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting but never committed; followed up several times and they eventually stopped responding.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K230" s="7" t="inlineStr"/>
@@ -11758,12 +11758,12 @@
       </c>
       <c r="I232" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J232" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K232" s="7" t="inlineStr"/>
@@ -11803,12 +11803,12 @@
       </c>
       <c r="I233" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J233" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K233" s="4" t="inlineStr"/>
@@ -11848,12 +11848,12 @@
       </c>
       <c r="I234" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J234" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K234" s="7" t="inlineStr"/>
@@ -11893,12 +11893,12 @@
       </c>
       <c r="I235" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J235" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K235" s="4" t="inlineStr"/>
@@ -11940,7 +11940,7 @@
           <t>Had Meeting - Interested</t>
         </is>
       </c>
-      <c r="I236" s="11" t="inlineStr">
+      <c r="I236" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="I238" s="10" t="inlineStr">
         <is>
-          <t>Ghosted</t>
+          <t>Maybe Later</t>
         </is>
       </c>
       <c r="J238" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting but never scheduled despite repeated follow-ups — went quiet.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K238" s="7" t="inlineStr"/>
@@ -12181,14 +12181,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I241" s="11" t="inlineStr">
+      <c r="I241" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J241" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no decision yet. Continuing to follow up — still warm.</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K241" s="4" t="inlineStr"/>
@@ -12226,7 +12226,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I242" s="10" t="inlineStr">
+      <c r="I242" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -12267,14 +12267,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I243" s="11" t="inlineStr">
+      <c r="I243" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J243" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K243" s="4" t="inlineStr"/>
@@ -12312,14 +12312,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I244" s="11" t="inlineStr">
+      <c r="I244" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J244" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K244" s="7" t="inlineStr"/>
@@ -12357,14 +12357,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I245" s="11" t="inlineStr">
+      <c r="I245" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J245" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K245" s="4" t="inlineStr"/>
@@ -12402,14 +12402,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I246" s="11" t="inlineStr">
+      <c r="I246" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J246" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K246" s="7" t="inlineStr"/>
@@ -12447,7 +12447,7 @@
           <t>Meeting Scheduled</t>
         </is>
       </c>
-      <c r="I247" s="11" t="inlineStr">
+      <c r="I247" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -12492,14 +12492,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I248" s="11" t="inlineStr">
+      <c r="I248" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J248" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K248" s="7" t="inlineStr"/>
@@ -12590,7 +12590,7 @@
           <t>Meeting Scheduled</t>
         </is>
       </c>
-      <c r="I250" s="11" t="inlineStr">
+      <c r="I250" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -12635,7 +12635,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I251" s="10" t="inlineStr">
+      <c r="I251" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -12680,14 +12680,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I252" s="11" t="inlineStr">
+      <c r="I252" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J252" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K252" s="7" t="inlineStr"/>
@@ -12729,14 +12729,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I253" s="11" t="inlineStr">
+      <c r="I253" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J253" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K253" s="4" t="inlineStr"/>
@@ -12880,14 +12880,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I256" s="11" t="inlineStr">
+      <c r="I256" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J256" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K256" s="7" t="inlineStr"/>
@@ -13174,14 +13174,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I262" s="11" t="inlineStr">
+      <c r="I262" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J262" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K262" s="7" t="inlineStr"/>
@@ -13215,14 +13215,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I263" s="11" t="inlineStr">
+      <c r="I263" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J263" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K263" s="4" t="inlineStr"/>
@@ -13305,14 +13305,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I265" s="11" t="inlineStr">
+      <c r="I265" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J265" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K265" s="4" t="inlineStr"/>
@@ -13350,14 +13350,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I266" s="11" t="inlineStr">
+      <c r="I266" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J266" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K266" s="7" t="inlineStr"/>
@@ -13440,7 +13440,7 @@
           <t>Meeting Scheduled</t>
         </is>
       </c>
-      <c r="I268" s="11" t="inlineStr">
+      <c r="I268" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13526,7 +13526,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I270" s="10" t="inlineStr">
+      <c r="I270" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -13571,7 +13571,7 @@
           <t>Had Meeting - Interested</t>
         </is>
       </c>
-      <c r="I271" s="11" t="inlineStr">
+      <c r="I271" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13616,7 +13616,7 @@
           <t>Had Meeting - Interested</t>
         </is>
       </c>
-      <c r="I272" s="11" t="inlineStr">
+      <c r="I272" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13653,14 +13653,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I273" s="11" t="inlineStr">
+      <c r="I273" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J273" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K273" s="4" t="inlineStr"/>
@@ -13690,14 +13690,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I274" s="11" t="inlineStr">
+      <c r="I274" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J274" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K274" s="7" t="inlineStr"/>
@@ -13727,7 +13727,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I275" s="10" t="inlineStr">
+      <c r="I275" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -13764,14 +13764,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I276" s="11" t="inlineStr">
+      <c r="I276" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J276" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K276" s="7" t="inlineStr"/>
@@ -13805,7 +13805,7 @@
           <t>Had Meeting - Interested</t>
         </is>
       </c>
-      <c r="I277" s="11" t="inlineStr">
+      <c r="I277" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13928,7 +13928,7 @@
           <t>Had Meeting - Interested</t>
         </is>
       </c>
-      <c r="I280" s="11" t="inlineStr">
+      <c r="I280" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13965,14 +13965,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I281" s="11" t="inlineStr">
+      <c r="I281" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J281" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K281" s="4" t="inlineStr"/>
@@ -14002,14 +14002,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I282" s="11" t="inlineStr">
+      <c r="I282" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J282" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K282" s="7" t="inlineStr"/>
@@ -14043,7 +14043,7 @@
           <t>Had Meeting - Interested</t>
         </is>
       </c>
-      <c r="I283" s="11" t="inlineStr">
+      <c r="I283" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -14162,14 +14162,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I286" s="11" t="inlineStr">
+      <c r="I286" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J286" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K286" s="7" t="inlineStr"/>
@@ -14199,14 +14199,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I287" s="11" t="inlineStr">
+      <c r="I287" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J287" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K287" s="4" t="inlineStr"/>
@@ -14240,14 +14240,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I288" s="11" t="inlineStr">
+      <c r="I288" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J288" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no decision yet. Continuing to follow up — still warm. Note: Only wanted very specifc workers comp cases. Also do personal injury but trying to focus on WC, follow up about personal injury in a month</t>
+          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play. Note: Only wanted very specifc workers comp cases. Also do personal injury but trying to focus on WC, follow up about personal injury in a month</t>
         </is>
       </c>
       <c r="K288" s="7" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I289" s="10" t="inlineStr">
+      <c r="I289" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -14314,14 +14314,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I290" s="11" t="inlineStr">
+      <c r="I290" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J290" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K290" s="7" t="inlineStr"/>
@@ -14355,7 +14355,7 @@
           <t>Had Meeting - Interested</t>
         </is>
       </c>
-      <c r="I291" s="11" t="inlineStr">
+      <c r="I291" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -14515,14 +14515,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I295" s="11" t="inlineStr">
+      <c r="I295" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J295" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K295" s="4" t="inlineStr"/>
@@ -14552,7 +14552,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I296" s="10" t="inlineStr">
+      <c r="I296" s="11" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -14589,14 +14589,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I297" s="11" t="inlineStr">
+      <c r="I297" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J297" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K297" s="4" t="inlineStr"/>
@@ -14626,14 +14626,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I298" s="11" t="inlineStr">
+      <c r="I298" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J298" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K298" s="7" t="inlineStr"/>
@@ -14663,14 +14663,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I299" s="11" t="inlineStr">
+      <c r="I299" s="10" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J299" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to get it on the calendar.</t>
+          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
         </is>
       </c>
       <c r="K299" s="4" t="inlineStr"/>
@@ -14745,11 +14745,11 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>38</v>
+        <v>191</v>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -14760,11 +14760,11 @@
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
     </row>
@@ -14844,7 +14844,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>38</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15">
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="B16" s="22" t="n">
-        <v>173</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -14979,7 +14979,7 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>Still in play — had a meeting and is considering, is interested, has a meeting on the books, or is a recent lead still being worked.</t>
+          <t>Still in play — had a meeting and is considering, showed interest, has a meeting on the books, or is being actively followed up to schedule.</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Went silent — booked a meeting and no-showed, or asked for a meeting / showed interest but stopped responding and never converted.</t>
+          <t>Booked a meeting and did not show, then went unresponsive to rebooking attempts.</t>
         </is>
       </c>
     </row>

--- a/MBP_Cold_Email_Follow_Up_Report.xlsx
+++ b/MBP_Cold_Email_Follow_Up_Report.xlsx
@@ -54,11 +54,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C6500"/>
+      <color rgb="003F3F3F"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="003F3F3F"/>
+      <color rgb="009C6500"/>
     </font>
     <font>
       <b val="1"/>
@@ -125,12 +125,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -202,8 +202,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,13 +223,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2720,14 +2720,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr"/>
@@ -2767,12 +2767,12 @@
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr"/>
@@ -2812,12 +2812,12 @@
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
@@ -2857,12 +2857,12 @@
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr"/>
@@ -2904,14 +2904,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr"/>
@@ -2953,14 +2953,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr"/>
@@ -3002,14 +3002,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr"/>
@@ -3049,12 +3049,12 @@
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr"/>
@@ -3096,14 +3096,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr"/>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr"/>
@@ -3188,12 +3188,12 @@
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr"/>
@@ -3284,14 +3284,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr"/>
@@ -3333,14 +3333,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr"/>
@@ -3380,12 +3380,12 @@
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr"/>
@@ -3425,12 +3425,12 @@
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr"/>
@@ -3472,14 +3472,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr"/>
@@ -3519,12 +3519,12 @@
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr"/>
@@ -3564,12 +3564,12 @@
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr"/>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="I59" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr"/>
@@ -3656,14 +3656,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr"/>
@@ -3705,14 +3705,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr"/>
@@ -3754,14 +3754,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr"/>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr"/>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr"/>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr"/>
@@ -3936,12 +3936,12 @@
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr"/>
@@ -3981,12 +3981,12 @@
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr"/>
@@ -4028,14 +4028,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I68" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr"/>
@@ -4077,14 +4077,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I69" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr"/>
@@ -4124,12 +4124,12 @@
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr"/>
@@ -4171,14 +4171,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I71" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr"/>
@@ -4220,14 +4220,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I72" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr"/>
@@ -4269,14 +4269,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr"/>
@@ -4316,12 +4316,12 @@
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr"/>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr"/>
@@ -4406,12 +4406,12 @@
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J76" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K76" s="7" t="inlineStr"/>
@@ -4453,14 +4453,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr"/>
@@ -4502,14 +4502,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K78" s="7" t="inlineStr"/>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J80" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K80" s="7" t="inlineStr"/>
@@ -4645,14 +4645,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr"/>
@@ -4692,12 +4692,12 @@
       </c>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J82" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K82" s="7" t="inlineStr"/>
@@ -4739,14 +4739,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I83" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr"/>
@@ -4786,12 +4786,12 @@
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K84" s="7" t="inlineStr"/>
@@ -4831,12 +4831,12 @@
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr"/>
@@ -4876,12 +4876,12 @@
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J86" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K86" s="7" t="inlineStr"/>
@@ -4921,12 +4921,12 @@
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr"/>
@@ -4966,12 +4966,12 @@
       </c>
       <c r="I88" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K88" s="7" t="inlineStr"/>
@@ -5013,14 +5013,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I89" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr"/>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="I90" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K90" s="7" t="inlineStr"/>
@@ -5107,14 +5107,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I91" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr"/>
@@ -5154,12 +5154,12 @@
       </c>
       <c r="I92" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr"/>
@@ -5199,12 +5199,12 @@
       </c>
       <c r="I93" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr"/>
@@ -5246,14 +5246,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I94" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr"/>
@@ -5295,14 +5295,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I95" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr"/>
@@ -5342,12 +5342,12 @@
       </c>
       <c r="I96" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K96" s="7" t="inlineStr"/>
@@ -5389,14 +5389,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I97" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr"/>
@@ -5436,12 +5436,12 @@
       </c>
       <c r="I98" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J98" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K98" s="7" t="inlineStr"/>
@@ -5481,12 +5481,12 @@
       </c>
       <c r="I99" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr"/>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="I100" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K100" s="7" t="inlineStr"/>
@@ -5573,14 +5573,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I101" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr"/>
@@ -5679,14 +5679,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I103" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr"/>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="I104" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K104" s="7" t="inlineStr"/>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="I105" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr"/>
@@ -5816,12 +5816,12 @@
       </c>
       <c r="I106" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K106" s="7" t="inlineStr"/>
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I107" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr"/>
@@ -5906,12 +5906,12 @@
       </c>
       <c r="I108" s="10" t="inlineStr">
         <is>
-          <t>Maybe Later</t>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K108" s="7" t="inlineStr"/>
@@ -5949,7 +5949,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I109" s="11" t="inlineStr">
+      <c r="I109" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -5998,14 +5998,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I110" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K110" s="7" t="inlineStr"/>
@@ -6043,14 +6043,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I111" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr"/>
@@ -6092,14 +6092,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I112" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K112" s="7" t="inlineStr"/>
@@ -6137,7 +6137,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I113" s="11" t="inlineStr">
+      <c r="I113" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -6182,14 +6182,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I114" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K114" s="7" t="inlineStr"/>
@@ -6227,14 +6227,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I115" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr"/>
@@ -6272,14 +6272,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I116" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K116" s="7" t="inlineStr"/>
@@ -6321,14 +6321,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I117" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr"/>
@@ -6366,14 +6366,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I118" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K118" s="7" t="inlineStr"/>
@@ -6411,14 +6411,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I119" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr"/>
@@ -6460,14 +6460,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I120" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K120" s="7" t="inlineStr"/>
@@ -6505,14 +6505,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I121" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr"/>
@@ -6550,14 +6550,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I122" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K122" s="7" t="inlineStr"/>
@@ -6595,14 +6595,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I123" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr"/>
@@ -6640,14 +6640,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I124" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K124" s="7" t="inlineStr"/>
@@ -6685,14 +6685,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I125" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr"/>
@@ -6779,14 +6779,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I127" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr"/>
@@ -6885,14 +6885,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I129" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr"/>
@@ -6930,14 +6930,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I130" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K130" s="7" t="inlineStr"/>
@@ -6975,14 +6975,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I131" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr"/>
@@ -7024,14 +7024,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I132" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I132" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K132" s="7" t="inlineStr"/>
@@ -7069,14 +7069,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I133" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr"/>
@@ -7118,14 +7118,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I134" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K134" s="7" t="inlineStr"/>
@@ -7216,14 +7216,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I136" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J136" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K136" s="7" t="inlineStr"/>
@@ -7261,14 +7261,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I137" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr"/>
@@ -7310,14 +7310,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I138" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J138" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K138" s="7" t="inlineStr"/>
@@ -7355,14 +7355,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I139" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr"/>
@@ -7404,14 +7404,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I140" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J140" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K140" s="7" t="inlineStr"/>
@@ -7453,14 +7453,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I141" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr"/>
@@ -7547,14 +7547,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I143" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J143" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr"/>
@@ -7592,7 +7592,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I144" s="11" t="inlineStr">
+      <c r="I144" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -7641,14 +7641,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I145" s="10" t="inlineStr">
+      <c r="I145" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J145" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr"/>
@@ -7690,14 +7690,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I146" s="10" t="inlineStr">
+      <c r="I146" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J146" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K146" s="7" t="inlineStr"/>
@@ -7735,14 +7735,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I147" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J147" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr"/>
@@ -7780,14 +7780,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I148" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I148" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K148" s="7" t="inlineStr"/>
@@ -7825,14 +7825,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I149" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J149" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr"/>
@@ -7874,14 +7874,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I150" s="10" t="inlineStr">
+      <c r="I150" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K150" s="7" t="inlineStr"/>
@@ -7923,14 +7923,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I151" s="10" t="inlineStr">
+      <c r="I151" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J151" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr"/>
@@ -7972,14 +7972,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I152" s="10" t="inlineStr">
+      <c r="I152" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J152" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K152" s="7" t="inlineStr"/>
@@ -8123,14 +8123,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I155" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I155" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J155" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr"/>
@@ -8217,14 +8217,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I157" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I157" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J157" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr"/>
@@ -8266,14 +8266,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I158" s="10" t="inlineStr">
+      <c r="I158" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J158" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K158" s="7" t="inlineStr"/>
@@ -8315,14 +8315,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I159" s="10" t="inlineStr">
+      <c r="I159" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J159" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr"/>
@@ -8364,14 +8364,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I160" s="10" t="inlineStr">
+      <c r="I160" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J160" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K160" s="7" t="inlineStr"/>
@@ -8409,14 +8409,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I161" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I161" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J161" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr"/>
@@ -8454,14 +8454,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I162" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I162" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J162" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K162" s="7" t="inlineStr"/>
@@ -8499,14 +8499,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I163" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I163" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J163" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr"/>
@@ -8544,14 +8544,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I164" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I164" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J164" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K164" s="7" t="inlineStr"/>
@@ -8589,14 +8589,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I165" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I165" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J165" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr"/>
@@ -8634,14 +8634,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I166" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I166" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J166" s="8" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K166" s="7" t="inlineStr"/>
@@ -8683,14 +8683,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I167" s="10" t="inlineStr">
+      <c r="I167" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J167" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr"/>
@@ -8732,14 +8732,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I168" s="10" t="inlineStr">
+      <c r="I168" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J168" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K168" s="7" t="inlineStr"/>
@@ -8777,14 +8777,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I169" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I169" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J169" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I170" s="11" t="inlineStr">
+      <c r="I170" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -8916,14 +8916,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I172" s="10" t="inlineStr">
+      <c r="I172" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J172" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K172" s="7" t="inlineStr"/>
@@ -8961,14 +8961,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I173" s="10" t="inlineStr">
-        <is>
-          <t>Maybe Later</t>
+      <c r="I173" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J173" s="6" t="inlineStr">
         <is>
-          <t>Replied positively and asked for a meeting; following up to lock in a time — open, warm lead.</t>
+          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr"/>
@@ -9096,7 +9096,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I176" s="10" t="inlineStr">
+      <c r="I176" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -9190,7 +9190,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I178" s="10" t="inlineStr">
+      <c r="I178" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -9288,14 +9288,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I180" s="10" t="inlineStr">
+      <c r="I180" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J180" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play. Note: Check in Q2 2026</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play. Note: Check in Q2 2026</t>
         </is>
       </c>
       <c r="K180" s="7" t="inlineStr"/>
@@ -9333,7 +9333,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I181" s="10" t="inlineStr">
+      <c r="I181" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -9382,14 +9382,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I182" s="10" t="inlineStr">
+      <c r="I182" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play. Note: Check in Q2 2026</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play. Note: Check in Q2 2026</t>
         </is>
       </c>
       <c r="K182" s="7" t="inlineStr"/>
@@ -9480,14 +9480,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I184" s="10" t="inlineStr">
+      <c r="I184" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K184" s="7" t="inlineStr"/>
@@ -9574,7 +9574,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I186" s="10" t="inlineStr">
+      <c r="I186" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -9619,7 +9619,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I187" s="11" t="inlineStr">
+      <c r="I187" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -9668,14 +9668,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I188" s="10" t="inlineStr">
+      <c r="I188" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K188" s="7" t="inlineStr"/>
@@ -9713,7 +9713,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I189" s="11" t="inlineStr">
+      <c r="I189" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -9758,7 +9758,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I190" s="10" t="inlineStr">
+      <c r="I190" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -9807,14 +9807,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I191" s="10" t="inlineStr">
+      <c r="I191" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J191" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K191" s="4" t="inlineStr"/>
@@ -9905,14 +9905,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I193" s="10" t="inlineStr">
+      <c r="I193" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J193" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K193" s="4" t="inlineStr"/>
@@ -9999,7 +9999,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I195" s="11" t="inlineStr">
+      <c r="I195" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -10101,7 +10101,7 @@
           <t>Meeting Scheduled</t>
         </is>
       </c>
-      <c r="I197" s="10" t="inlineStr">
+      <c r="I197" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -10146,7 +10146,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I198" s="11" t="inlineStr">
+      <c r="I198" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -10191,14 +10191,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I199" s="10" t="inlineStr">
+      <c r="I199" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J199" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K199" s="4" t="inlineStr"/>
@@ -10240,14 +10240,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I200" s="10" t="inlineStr">
+      <c r="I200" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J200" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K200" s="7" t="inlineStr"/>
@@ -10285,7 +10285,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I201" s="10" t="inlineStr">
+      <c r="I201" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -10330,7 +10330,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I202" s="11" t="inlineStr">
+      <c r="I202" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -10375,7 +10375,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I203" s="10" t="inlineStr">
+      <c r="I203" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -10477,7 +10477,7 @@
           <t>Meeting Scheduled</t>
         </is>
       </c>
-      <c r="I205" s="10" t="inlineStr">
+      <c r="I205" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -10526,14 +10526,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I206" s="10" t="inlineStr">
+      <c r="I206" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J206" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K206" s="7" t="inlineStr"/>
@@ -10571,7 +10571,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I207" s="10" t="inlineStr">
+      <c r="I207" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -10616,7 +10616,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I208" s="10" t="inlineStr">
+      <c r="I208" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -10661,7 +10661,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I209" s="11" t="inlineStr">
+      <c r="I209" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -10755,7 +10755,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I211" s="10" t="inlineStr">
+      <c r="I211" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -10800,7 +10800,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I212" s="10" t="inlineStr">
+      <c r="I212" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -10841,7 +10841,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I213" s="11" t="inlineStr">
+      <c r="I213" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -10947,14 +10947,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I215" s="10" t="inlineStr">
+      <c r="I215" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J215" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K215" s="4" t="inlineStr"/>
@@ -10992,7 +10992,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I216" s="10" t="inlineStr">
+      <c r="I216" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -11037,7 +11037,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I217" s="10" t="inlineStr">
+      <c r="I217" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -11082,7 +11082,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I218" s="10" t="inlineStr">
+      <c r="I218" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -11131,14 +11131,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I219" s="10" t="inlineStr">
+      <c r="I219" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J219" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K219" s="4" t="inlineStr"/>
@@ -11176,7 +11176,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I220" s="11" t="inlineStr">
+      <c r="I220" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -11270,7 +11270,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I222" s="11" t="inlineStr">
+      <c r="I222" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -11319,14 +11319,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I223" s="10" t="inlineStr">
+      <c r="I223" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J223" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K223" s="4" t="inlineStr"/>
@@ -11364,7 +11364,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I224" s="11" t="inlineStr">
+      <c r="I224" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -11413,14 +11413,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I225" s="10" t="inlineStr">
+      <c r="I225" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J225" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K225" s="4" t="inlineStr"/>
@@ -11564,7 +11564,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I228" s="10" t="inlineStr">
+      <c r="I228" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -11662,14 +11662,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I230" s="10" t="inlineStr">
+      <c r="I230" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J230" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K230" s="7" t="inlineStr"/>
@@ -11756,7 +11756,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I232" s="10" t="inlineStr">
+      <c r="I232" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -11801,7 +11801,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I233" s="10" t="inlineStr">
+      <c r="I233" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -11846,7 +11846,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I234" s="10" t="inlineStr">
+      <c r="I234" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -11891,7 +11891,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I235" s="10" t="inlineStr">
+      <c r="I235" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -11940,7 +11940,7 @@
           <t>Had Meeting - Interested</t>
         </is>
       </c>
-      <c r="I236" s="10" t="inlineStr">
+      <c r="I236" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -12034,7 +12034,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I238" s="10" t="inlineStr">
+      <c r="I238" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -12181,14 +12181,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I241" s="10" t="inlineStr">
+      <c r="I241" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J241" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play.</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play.</t>
         </is>
       </c>
       <c r="K241" s="4" t="inlineStr"/>
@@ -12226,7 +12226,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I242" s="11" t="inlineStr">
+      <c r="I242" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -12267,7 +12267,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I243" s="10" t="inlineStr">
+      <c r="I243" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -12312,7 +12312,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I244" s="10" t="inlineStr">
+      <c r="I244" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -12357,7 +12357,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I245" s="10" t="inlineStr">
+      <c r="I245" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -12402,7 +12402,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I246" s="10" t="inlineStr">
+      <c r="I246" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -12447,7 +12447,7 @@
           <t>Meeting Scheduled</t>
         </is>
       </c>
-      <c r="I247" s="10" t="inlineStr">
+      <c r="I247" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -12492,7 +12492,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I248" s="10" t="inlineStr">
+      <c r="I248" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -12590,7 +12590,7 @@
           <t>Meeting Scheduled</t>
         </is>
       </c>
-      <c r="I250" s="10" t="inlineStr">
+      <c r="I250" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -12635,7 +12635,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I251" s="11" t="inlineStr">
+      <c r="I251" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -12680,7 +12680,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I252" s="10" t="inlineStr">
+      <c r="I252" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -12729,7 +12729,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I253" s="10" t="inlineStr">
+      <c r="I253" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -12880,7 +12880,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I256" s="10" t="inlineStr">
+      <c r="I256" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13174,7 +13174,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I262" s="10" t="inlineStr">
+      <c r="I262" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13215,7 +13215,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I263" s="10" t="inlineStr">
+      <c r="I263" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13305,7 +13305,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I265" s="10" t="inlineStr">
+      <c r="I265" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13350,7 +13350,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I266" s="10" t="inlineStr">
+      <c r="I266" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13440,7 +13440,7 @@
           <t>Meeting Scheduled</t>
         </is>
       </c>
-      <c r="I268" s="10" t="inlineStr">
+      <c r="I268" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13526,7 +13526,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I270" s="11" t="inlineStr">
+      <c r="I270" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -13571,7 +13571,7 @@
           <t>Had Meeting - Interested</t>
         </is>
       </c>
-      <c r="I271" s="10" t="inlineStr">
+      <c r="I271" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13616,7 +13616,7 @@
           <t>Had Meeting - Interested</t>
         </is>
       </c>
-      <c r="I272" s="10" t="inlineStr">
+      <c r="I272" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13653,7 +13653,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I273" s="10" t="inlineStr">
+      <c r="I273" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13690,7 +13690,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I274" s="10" t="inlineStr">
+      <c r="I274" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13727,7 +13727,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I275" s="11" t="inlineStr">
+      <c r="I275" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -13764,7 +13764,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I276" s="10" t="inlineStr">
+      <c r="I276" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13805,7 +13805,7 @@
           <t>Had Meeting - Interested</t>
         </is>
       </c>
-      <c r="I277" s="10" t="inlineStr">
+      <c r="I277" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13928,7 +13928,7 @@
           <t>Had Meeting - Interested</t>
         </is>
       </c>
-      <c r="I280" s="10" t="inlineStr">
+      <c r="I280" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -13965,7 +13965,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I281" s="10" t="inlineStr">
+      <c r="I281" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -14002,7 +14002,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I282" s="10" t="inlineStr">
+      <c r="I282" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -14043,7 +14043,7 @@
           <t>Had Meeting - Interested</t>
         </is>
       </c>
-      <c r="I283" s="10" t="inlineStr">
+      <c r="I283" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -14162,7 +14162,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I286" s="10" t="inlineStr">
+      <c r="I286" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -14199,7 +14199,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I287" s="10" t="inlineStr">
+      <c r="I287" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -14240,14 +14240,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I288" s="10" t="inlineStr">
+      <c r="I288" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
       </c>
       <c r="J288" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting; no signed decision yet. Actively following up to move it forward — still in play. Note: Only wanted very specifc workers comp cases. Also do personal injury but trying to focus on WC, follow up about personal injury in a month</t>
+          <t>Had the meeting; no signed decision yet. Following up to move it forward — still in play. Note: Only wanted very specifc workers comp cases. Also do personal injury but trying to focus on WC, follow up about personal injury in a month</t>
         </is>
       </c>
       <c r="K288" s="7" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I289" s="11" t="inlineStr">
+      <c r="I289" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -14314,7 +14314,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I290" s="10" t="inlineStr">
+      <c r="I290" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -14355,7 +14355,7 @@
           <t>Had Meeting - Interested</t>
         </is>
       </c>
-      <c r="I291" s="10" t="inlineStr">
+      <c r="I291" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -14515,7 +14515,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I295" s="10" t="inlineStr">
+      <c r="I295" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -14552,7 +14552,7 @@
           <t>Meeting No Show</t>
         </is>
       </c>
-      <c r="I296" s="11" t="inlineStr">
+      <c r="I296" s="10" t="inlineStr">
         <is>
           <t>Ghosted</t>
         </is>
@@ -14589,7 +14589,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I297" s="10" t="inlineStr">
+      <c r="I297" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -14626,7 +14626,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I298" s="10" t="inlineStr">
+      <c r="I298" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -14663,7 +14663,7 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I299" s="10" t="inlineStr">
+      <c r="I299" s="11" t="inlineStr">
         <is>
           <t>Maybe Later</t>
         </is>
@@ -14745,11 +14745,11 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>191</v>
+        <v>83</v>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>28.1%</t>
         </is>
       </c>
     </row>
@@ -14760,11 +14760,11 @@
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -14775,11 +14775,11 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>38.0%</t>
         </is>
       </c>
     </row>
@@ -14844,7 +14844,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>191</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
@@ -14854,7 +14854,7 @@
         </is>
       </c>
       <c r="B15" s="22" t="n">
-        <v>43</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="B16" s="22" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">

--- a/MBP_Cold_Email_Follow_Up_Report.xlsx
+++ b/MBP_Cold_Email_Follow_Up_Report.xlsx
@@ -2720,14 +2720,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr"/>
@@ -2904,14 +2904,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr"/>
@@ -2953,14 +2953,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr"/>
@@ -3002,14 +3002,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr"/>
@@ -3096,14 +3096,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr"/>
@@ -3284,14 +3284,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr"/>
@@ -3333,14 +3333,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr"/>
@@ -3472,14 +3472,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr"/>
@@ -3656,14 +3656,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr"/>
@@ -3705,14 +3705,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr"/>
@@ -3754,14 +3754,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr"/>
@@ -4028,14 +4028,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr"/>
@@ -4077,14 +4077,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr"/>
@@ -4171,14 +4171,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr"/>
@@ -4220,14 +4220,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I72" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr"/>
@@ -4269,14 +4269,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr"/>
@@ -4453,14 +4453,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr"/>
@@ -4502,14 +4502,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K78" s="7" t="inlineStr"/>
@@ -4645,14 +4645,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr"/>
@@ -4739,14 +4739,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr"/>
@@ -5013,14 +5013,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I89" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr"/>
@@ -5107,14 +5107,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I91" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr"/>
@@ -5246,14 +5246,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I94" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr"/>
@@ -5295,14 +5295,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr"/>
@@ -5389,14 +5389,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr"/>
@@ -5573,14 +5573,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr"/>
@@ -5679,14 +5679,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr"/>
@@ -5998,14 +5998,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I110" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I110" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K110" s="7" t="inlineStr"/>
@@ -6043,14 +6043,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I111" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I111" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr"/>
@@ -6092,14 +6092,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I112" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I112" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K112" s="7" t="inlineStr"/>
@@ -6182,14 +6182,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I114" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I114" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K114" s="7" t="inlineStr"/>
@@ -6227,14 +6227,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I115" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I115" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr"/>
@@ -6272,14 +6272,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I116" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I116" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K116" s="7" t="inlineStr"/>
@@ -6321,14 +6321,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I117" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I117" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr"/>
@@ -6366,14 +6366,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I118" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K118" s="7" t="inlineStr"/>
@@ -6411,14 +6411,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I119" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I119" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr"/>
@@ -6460,14 +6460,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I120" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I120" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K120" s="7" t="inlineStr"/>
@@ -6505,14 +6505,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I121" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I121" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr"/>
@@ -6550,14 +6550,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I122" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I122" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K122" s="7" t="inlineStr"/>
@@ -6595,14 +6595,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I123" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I123" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr"/>
@@ -6640,14 +6640,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I124" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I124" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K124" s="7" t="inlineStr"/>
@@ -6685,14 +6685,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I125" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I125" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr"/>
@@ -6779,14 +6779,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I127" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr"/>
@@ -6885,14 +6885,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I129" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I129" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr"/>
@@ -6930,14 +6930,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I130" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I130" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K130" s="7" t="inlineStr"/>
@@ -6975,14 +6975,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I131" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I131" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr"/>
@@ -7024,14 +7024,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I132" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I132" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K132" s="7" t="inlineStr"/>
@@ -7069,14 +7069,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I133" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I133" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr"/>
@@ -7118,14 +7118,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I134" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I134" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K134" s="7" t="inlineStr"/>
@@ -7216,14 +7216,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I136" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I136" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J136" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K136" s="7" t="inlineStr"/>
@@ -7261,14 +7261,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I137" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I137" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr"/>
@@ -7310,14 +7310,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I138" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I138" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J138" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K138" s="7" t="inlineStr"/>
@@ -7355,14 +7355,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I139" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I139" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr"/>
@@ -7404,14 +7404,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I140" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I140" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J140" s="8" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K140" s="7" t="inlineStr"/>
@@ -7453,14 +7453,14 @@
           <t>Had Meeting</t>
         </is>
       </c>
-      <c r="I141" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I141" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>Had the meeting and followed up multiple times afterward; did not move forward — closed-lost.</t>
+          <t>Had the meeting, then went quiet; followed up multiple times afterward with no response — written off.</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr"/>
@@ -7547,14 +7547,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I143" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I143" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J143" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr"/>
@@ -7735,14 +7735,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I147" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I147" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J147" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr"/>
@@ -7780,14 +7780,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I148" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I148" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K148" s="7" t="inlineStr"/>
@@ -7825,14 +7825,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I149" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I149" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J149" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr"/>
@@ -8123,14 +8123,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I155" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I155" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J155" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr"/>
@@ -8217,14 +8217,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I157" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I157" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J157" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr"/>
@@ -8409,14 +8409,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I161" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I161" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J161" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr"/>
@@ -8454,14 +8454,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I162" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I162" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J162" s="8" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K162" s="7" t="inlineStr"/>
@@ -8499,14 +8499,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I163" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I163" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J163" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr"/>
@@ -8544,14 +8544,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I164" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I164" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J164" s="8" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K164" s="7" t="inlineStr"/>
@@ -8589,14 +8589,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I165" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I165" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J165" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr"/>
@@ -8634,14 +8634,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I166" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I166" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J166" s="8" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K166" s="7" t="inlineStr"/>
@@ -8777,14 +8777,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I169" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I169" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J169" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr"/>
@@ -8961,14 +8961,14 @@
           <t>Interested</t>
         </is>
       </c>
-      <c r="I173" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I173" s="10" t="inlineStr">
+        <is>
+          <t>Ghosted</t>
         </is>
       </c>
       <c r="J173" s="6" t="inlineStr">
         <is>
-          <t>Showed interest and was followed up with repeatedly; never scheduled and did not move forward — closed-lost.</t>
+          <t>Replied positively but never booked; followed up multiple times over several weeks and never got a response — went silent.</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr"/>
@@ -14760,11 +14760,11 @@
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>43.4%</t>
         </is>
       </c>
     </row>
@@ -14775,11 +14775,11 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -14854,7 +14854,7 @@
         </is>
       </c>
       <c r="B15" s="22" t="n">
-        <v>112</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="B16" s="22" t="n">
-        <v>59</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>Declined — not interested after contact, or signed then cancelled.</t>
+          <t>Explicitly declined — said they were not interested after contact, or signed then cancelled.</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Booked a meeting and did not show, then went unresponsive to rebooking attempts.</t>
+          <t>Replied positively or met, then stopped responding to repeated follow-ups and never came back — written off.</t>
         </is>
       </c>
     </row>
